--- a/data/trans_orig/IP09B02-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP09B02-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio en 2007 (tasa de respuesta: 98,55%)</t>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio como pasear, ir al cine, hacer deporte, etc en 2007 (tasa de respuesta: 98,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>3976</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8557</t>
+          <t>8662</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7349</t>
+          <t>7318</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12773</t>
+          <t>13098</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19221</t>
+          <t>19214</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,36%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5906</t>
+          <t>5813</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4125</t>
+          <t>4156</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8491</t>
+          <t>8166</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>38,4%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2708</t>
+          <t>2401</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>3305</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7964</t>
+          <t>7985</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8020</t>
+          <t>7933</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14071</t>
+          <t>14099</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>86,01%</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4996</t>
+          <t>5303</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>702</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5407</t>
+          <t>5382</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>61,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2321</t>
+          <t>2293</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8372</t>
+          <t>8459</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>51,6%</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9801</t>
+          <t>9845</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13043</t>
+          <t>13108</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4070</t>
+          <t>4026</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4671</t>
+          <t>4606</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,0%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7107</t>
+          <t>7127</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13704</t>
+          <t>13417</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13954</t>
+          <t>14522</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23170</t>
+          <t>23252</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31855</t>
+          <t>31921</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>85,27%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10303</t>
+          <t>10283</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6070</t>
+          <t>5502</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5579</t>
+          <t>5513</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14264</t>
+          <t>14182</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>37,89%</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5819</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>66,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7572</t>
+          <t>7492</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13526</t>
+          <t>13516</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14818</t>
+          <t>15401</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21727</t>
+          <t>21648</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,24%</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3619</t>
+          <t>2930</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7936</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2531</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9440</t>
+          <t>8857</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>36,51%</t>
         </is>
       </c>
     </row>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4400</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7190</t>
+          <t>6909</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11893</t>
+          <t>11885</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,7%</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3527</t>
+          <t>3394</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>4009</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>665</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5360</t>
+          <t>5641</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>44,95%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32059</t>
+          <t>32345</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42814</t>
+          <t>42665</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>56938</t>
+          <t>57120</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>68040</t>
+          <t>68058</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>93525</t>
+          <t>93210</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>108655</t>
+          <t>108426</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>83,65%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9306</t>
+          <t>9455</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>19775</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>9450</t>
+          <t>9432</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>20552</t>
+          <t>20370</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>20956</t>
+          <t>21185</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>36086</t>
+          <t>36401</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>28,08%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio en 2012 (tasa de respuesta: 97,74%)</t>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio como pasear, ir al cine, hacer deporte, etc en 2012 (tasa de respuesta: 97,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1887</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6030</t>
+          <t>6140</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2822</t>
+          <t>3190</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6833</t>
+          <t>6856</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6233</t>
+          <t>6116</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12238</t>
+          <t>12221</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,48%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>772</t>
+          <t>662</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>4792</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>638</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4672</t>
+          <t>4304</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>2075</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8063</t>
+          <t>8180</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>57,22%</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4344</t>
+          <t>4507</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1877</t>
+          <t>1861</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6290</t>
+          <t>6262</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7573</t>
+          <t>7620</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13910</t>
+          <t>13916</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>82,93%</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4131</t>
+          <t>3968</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6428</t>
+          <t>6444</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2870</t>
+          <t>2864</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9207</t>
+          <t>9160</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>54,59%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6021</t>
+          <t>6112</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5759</t>
+          <t>5338</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10853</t>
+          <t>10758</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8380</t>
+          <t>7964</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15985</t>
+          <t>15657</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>77,03%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2161</t>
+          <t>2070</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6883</t>
+          <t>6942</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6386</t>
+          <t>6807</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4342</t>
+          <t>4670</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11947</t>
+          <t>12363</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>60,82%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18061</t>
+          <t>18232</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27087</t>
+          <t>26792</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17390</t>
+          <t>17329</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27399</t>
+          <t>27463</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>38783</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>52058</t>
+          <t>52243</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>73,62%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6741</t>
+          <t>7036</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15767</t>
+          <t>15596</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9734</t>
+          <t>9670</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19743</t>
+          <t>19804</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,17%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18903</t>
+          <t>18718</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>32102</t>
+          <t>32178</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>45,35%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7855</t>
+          <t>7258</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14194</t>
+          <t>13679</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9236</t>
+          <t>9214</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17612</t>
+          <t>17182</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19134</t>
+          <t>19077</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29363</t>
+          <t>29054</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>72,63%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9513</t>
+          <t>10110</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>58,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5021</t>
+          <t>5451</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13397</t>
+          <t>13419</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10638</t>
+          <t>10947</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20867</t>
+          <t>20924</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>52,31%</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3687</t>
+          <t>3640</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2512</t>
+          <t>2952</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3522</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9244</t>
+          <t>9121</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>80,74%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3849</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2053</t>
+          <t>2176</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7775</t>
+          <t>7436</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>65,83%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>42876</t>
+          <t>42333</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>56691</t>
+          <t>56669</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>50773</t>
+          <t>50400</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>66862</t>
+          <t>66520</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>100024</t>
+          <t>98370</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>120897</t>
+          <t>119610</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>68,87%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>22900</t>
+          <t>22922</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>36715</t>
+          <t>37258</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>27210</t>
+          <t>27552</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>43299</t>
+          <t>43672</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>52765</t>
+          <t>54052</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>73638</t>
+          <t>75292</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>43,36%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio en 2016 (tasa de respuesta: 99,32%)</t>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio como pasear, ir al cine, hacer deporte, etc en 2016 (tasa de respuesta: 99,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>544</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4555</t>
+          <t>4163</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5461</t>
+          <t>5444</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2907</t>
+          <t>2734</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8521</t>
+          <t>8517</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,4%</t>
+          <t>66,36%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4814</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6172</t>
+          <t>6219</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4313</t>
+          <t>4317</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9927</t>
+          <t>10100</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>78,7%</t>
         </is>
       </c>
     </row>
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1795</t>
+          <t>1750</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6356</t>
+          <t>6503</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7228</t>
+          <t>7255</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>65,38%</t>
         </is>
       </c>
     </row>
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6736</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>3843</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9125</t>
+          <t>9133</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,29%</t>
         </is>
       </c>
     </row>
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>652</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4528</t>
+          <t>4510</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1732</t>
+          <t>1786</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6397</t>
+          <t>6419</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,8%</t>
         </is>
       </c>
     </row>
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5097</t>
+          <t>5092</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2648</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7335</t>
+          <t>7281</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>80,3%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>6775</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13314</t>
+          <t>12994</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6272</t>
+          <t>6190</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15501</t>
+          <t>15851</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22962</t>
+          <t>22961</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3098</t>
+          <t>3418</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9392</t>
+          <t>9637</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7185,7 +7185,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4681</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4403</t>
+          <t>4404</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11864</t>
+          <t>11514</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7235,7 +7235,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>42,07%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3666</t>
+          <t>3424</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9500</t>
+          <t>9526</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2858</t>
+          <t>2850</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7980</t>
+          <t>8008</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8235</t>
+          <t>7907</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16184</t>
+          <t>16076</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>67,95%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4249</t>
+          <t>4223</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10083</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7051</t>
+          <t>7059</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7474</t>
+          <t>7582</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15423</t>
+          <t>15751</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>66,58%</t>
         </is>
       </c>
     </row>
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5192</t>
+          <t>5189</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1458</t>
+          <t>1460</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6553</t>
+          <t>6602</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>65,72%</t>
         </is>
       </c>
     </row>
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1958</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6253</t>
+          <t>5859</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3493</t>
+          <t>3444</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8588</t>
+          <t>8586</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,46%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16795</t>
+          <t>16872</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26932</t>
+          <t>27308</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22301</t>
+          <t>22013</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33279</t>
+          <t>33638</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>41615</t>
+          <t>41456</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>57911</t>
+          <t>57885</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>61,54%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>17372</t>
+          <t>16996</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>27509</t>
+          <t>27432</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>16485</t>
+          <t>16126</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>27463</t>
+          <t>27751</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>36157</t>
+          <t>36183</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>52453</t>
+          <t>52612</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>55,93%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio como pasear, ir al cine, hacer deporte, etc en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6185</t>
+          <t>6214</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10095</t>
+          <t>10061</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4093</t>
+          <t>4144</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10612</t>
+          <t>10724</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11870</t>
+          <t>11895</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19554</t>
+          <t>19572</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,64%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>562</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4438</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3652</t>
+          <t>3540</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10171</t>
+          <t>10120</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5334</t>
+          <t>5316</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13018</t>
+          <t>12993</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>52,21%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3699</t>
+          <t>3497</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7607</t>
+          <t>7609</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6253</t>
+          <t>6226</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10781</t>
+          <t>10760</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12116</t>
+          <t>11300</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18093</t>
+          <t>17812</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>91,6%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>592</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4502</t>
+          <t>4704</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>482</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4989</t>
+          <t>5016</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>1632</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7328</t>
+          <t>8144</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>41,88%</t>
         </is>
       </c>
     </row>
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2958</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7315</t>
+          <t>7294</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4826</t>
+          <t>5133</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9825</t>
+          <t>9874</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,59%</t>
         </is>
       </c>
     </row>
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>474</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4810</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>61,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>455</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5503</t>
+          <t>5196</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>50,3%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15463</t>
+          <t>15607</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23475</t>
+          <t>23354</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>62,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18652</t>
+          <t>18559</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26946</t>
+          <t>27037</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36208</t>
+          <t>37735</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48409</t>
+          <t>49176</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>64,33%</t>
+          <t>67,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>87,37%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1580</t>
+          <t>1701</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9592</t>
+          <t>9448</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4282</t>
+          <t>4191</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12576</t>
+          <t>12669</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7874</t>
+          <t>7107</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>20075</t>
+          <t>18548</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>32,95%</t>
         </is>
       </c>
     </row>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8300</t>
+          <t>8568</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -10025,7 +10025,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>65,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -10045,7 +10045,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20731</t>
+          <t>20989</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -10060,7 +10060,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32276</t>
+          <t>31553</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38922</t>
+          <t>38830</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -10128,7 +10128,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4720</t>
+          <t>4452</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5765</t>
+          <t>5507</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>685</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7239</t>
+          <t>7962</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>20,15%</t>
         </is>
       </c>
     </row>
@@ -10353,7 +10353,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>727</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>470</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4142</t>
+          <t>4259</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7049</t>
+          <t>7172</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>73,71%</t>
         </is>
       </c>
     </row>
@@ -10471,7 +10471,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3641</t>
+          <t>3362</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1485</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5160</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>2557</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7803</t>
+          <t>7702</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>79,16%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>45028</t>
+          <t>45687</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>56624</t>
+          <t>56596</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>63486</t>
+          <t>63547</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>80674</t>
+          <t>80711</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>113803</t>
+          <t>113100</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>134268</t>
+          <t>133182</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>83,14%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6924</t>
+          <t>6952</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18520</t>
+          <t>17861</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>15965</t>
+          <t>15928</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>33153</t>
+          <t>33092</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>25919</t>
+          <t>27005</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>46384</t>
+          <t>47087</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,39%</t>
         </is>
       </c>
     </row>
